--- a/sample_users.xlsx
+++ b/sample_users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8610590cbf95aee3/Desktop/Darsh/thesis-scheduler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{DC5E2C1F-4682-4CFB-953B-1D88274790A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BCD9803-296D-49F3-B241-D23E7BA28209}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{DC5E2C1F-4682-4CFB-953B-1D88274790A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1477EB-142C-469D-8542-C74C74C95491}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{8312DD47-3CCB-43BC-A33E-BB7578786893}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="128">
   <si>
     <t>Name</t>
   </si>
@@ -173,9 +173,6 @@
     <t>Fatma Newagy</t>
   </si>
   <si>
-    <t>Gamal Abdel Shafy Ebrahim</t>
-  </si>
-  <si>
     <t>Gamal Eldin Mohamed Aly</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>Mohamed Hesham Farouk</t>
   </si>
   <si>
-    <t>Mohamed Refky Mohamed Amin</t>
-  </si>
-  <si>
     <t>Mohamed Rehan</t>
   </si>
   <si>
@@ -353,9 +347,6 @@
     <t>email38@example.com</t>
   </si>
   <si>
-    <t>email39@example.com</t>
-  </si>
-  <si>
     <t>email40@example.com</t>
   </si>
   <si>
@@ -429,6 +420,9 @@
   </si>
   <si>
     <t>email62@example.com</t>
+  </si>
+  <si>
+    <t>Mohamed Refky Mohamed</t>
   </si>
 </sst>
 </file>
@@ -533,10 +527,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -856,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="37.734375" bestFit="1" customWidth="1"/>
@@ -880,7 +870,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -891,7 +881,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -902,7 +892,7 @@
         <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -913,7 +903,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
@@ -924,7 +914,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -935,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -946,7 +936,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -957,7 +947,7 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -968,7 +958,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -979,7 +969,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>4</v>
@@ -990,7 +980,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>4</v>
@@ -1001,7 +991,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -1012,10 +1002,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1023,7 +1013,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1034,7 +1024,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1042,46 +1032,46 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1089,7 +1079,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1097,35 +1087,35 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1133,7 +1123,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1144,7 +1134,7 @@
         <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1155,7 +1145,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1165,8 +1155,8 @@
       <c r="A28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>113</v>
+      <c r="B28" t="s">
+        <v>111</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1177,7 +1167,7 @@
         <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1185,54 +1175,54 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
+        <v>21</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>113</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>116</v>
+        <v>22</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>4</v>
@@ -1240,10 +1230,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>4</v>
@@ -1251,32 +1241,32 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
+        <v>25</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>4</v>
@@ -1284,43 +1274,43 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>57</v>
+      </c>
+      <c r="B39" t="s">
+        <v>115</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" t="s">
-        <v>118</v>
+        <v>27</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1328,43 +1318,43 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>120</v>
+        <v>28</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>121</v>
+        <v>29</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>4</v>
@@ -1372,54 +1362,54 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>119</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
+        <v>31</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>31</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>91</v>
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>120</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" t="s">
-        <v>123</v>
+        <v>32</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>4</v>
@@ -1427,10 +1417,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>4</v>
@@ -1438,32 +1428,32 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>4</v>
@@ -1471,21 +1461,21 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>5</v>
@@ -1493,43 +1483,43 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>97</v>
+        <v>62</v>
+      </c>
+      <c r="B59" t="s">
+        <v>121</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61" t="s">
-        <v>125</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>3</v>
@@ -1537,35 +1527,24 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C62" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C49" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C61">
-      <sortCondition ref="A1:A49"/>
+  <autoFilter ref="A1:C48" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C60">
+      <sortCondition ref="A1:A48"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B62" r:id="rId1" xr:uid="{1DA225FB-8F48-4120-BB82-DB3C65C02DF5}"/>
-    <hyperlink ref="B63" r:id="rId2" xr:uid="{03646A07-246B-4A81-B6F7-921957311AD5}"/>
+    <hyperlink ref="B61" r:id="rId1" xr:uid="{1DA225FB-8F48-4120-BB82-DB3C65C02DF5}"/>
+    <hyperlink ref="B62" r:id="rId2" xr:uid="{03646A07-246B-4A81-B6F7-921957311AD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sample_users.xlsx
+++ b/sample_users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8610590cbf95aee3/Desktop/Darsh/thesis-scheduler/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosta_f0fjo8m\OneDrive\Desktop\Darsh\thesis-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{DC5E2C1F-4682-4CFB-953B-1D88274790A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1477EB-142C-469D-8542-C74C74C95491}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F684B2-7DDA-4477-AB72-9C180F2FD94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{8312DD47-3CCB-43BC-A33E-BB7578786893}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
   <si>
     <t>Name</t>
   </si>
@@ -59,183 +59,6 @@
     <t>BOTH</t>
   </si>
   <si>
-    <t>Mahmoud Ibrahim Khalil</t>
-  </si>
-  <si>
-    <t>Tamer Mostafa</t>
-  </si>
-  <si>
-    <t>Wagdy Anis Aziz</t>
-  </si>
-  <si>
-    <t>Walaa Gad</t>
-  </si>
-  <si>
-    <t>Ahmed Abd El-Hamid Mohamed Shafik Maarouf</t>
-  </si>
-  <si>
-    <t>Ahmed Mohammed Hassan Abdelfattah</t>
-  </si>
-  <si>
-    <t>Amr Abdallah Abou Shousha</t>
-  </si>
-  <si>
-    <t>Anke . Klingner</t>
-  </si>
-  <si>
-    <t>Catherine Malak Noshy Ibrahim Elias</t>
-  </si>
-  <si>
-    <t>Eman Ahmed Hamdy Azab</t>
-  </si>
-  <si>
-    <t>Gamal Abdel Shafy</t>
-  </si>
-  <si>
-    <t>Haitham Abdelsalam Ahmed Omran</t>
-  </si>
-  <si>
-    <t>Haytham Osman Ismail</t>
-  </si>
-  <si>
-    <t>Hisham Hassaballah Othman</t>
-  </si>
-  <si>
-    <t>Hossam Eldin Hassan Abdelmunim</t>
-  </si>
-  <si>
-    <t>Maggie Ahmed Ezzat Mashaly</t>
-  </si>
-  <si>
-    <t>Mervat Mustafa Fahmy Abuelkheir</t>
-  </si>
-  <si>
-    <t>Milad Michel Ghantous</t>
-  </si>
-  <si>
-    <t>Mohamed Abdel Ghany Ahmed Salem</t>
-  </si>
-  <si>
-    <t>Mohamed Ehsan Ashour</t>
-  </si>
-  <si>
-    <t>Mohamed Hamed Fahmy</t>
-  </si>
-  <si>
-    <t>Mohamed Kamel Gabr</t>
-  </si>
-  <si>
-    <t>Mohammed Abdel Megeed Salem</t>
-  </si>
-  <si>
-    <t>Nada Ahmed Hamed</t>
-  </si>
-  <si>
-    <t>Nourhan Ehab Azab</t>
-  </si>
-  <si>
-    <t>Rimon . Elias</t>
-  </si>
-  <si>
-    <t>Shereen Moataz Mahmoud Mohamed Afifi</t>
-  </si>
-  <si>
-    <t>Sherif Saad Mohamed Ahmed</t>
-  </si>
-  <si>
-    <t>Slim . Abdennadher</t>
-  </si>
-  <si>
-    <t>Wael Mohamed AbulSadat</t>
-  </si>
-  <si>
-    <t>Wael Zakaria Abdallah</t>
-  </si>
-  <si>
-    <t>Wassim Joseph Alexan</t>
-  </si>
-  <si>
-    <t>Ahmed Hassan Yousef</t>
-  </si>
-  <si>
-    <t>Ahmed Moh El Bialy</t>
-  </si>
-  <si>
-    <t>Amir Yassin Hassan Soliman</t>
-  </si>
-  <si>
-    <t>Azza Taha</t>
-  </si>
-  <si>
-    <t>Caroline Sabty</t>
-  </si>
-  <si>
-    <t>Fatma Newagy</t>
-  </si>
-  <si>
-    <t>Gamal Eldin Mohamed Aly</t>
-  </si>
-  <si>
-    <t>Haana Bayoumi Ali Mobarez</t>
-  </si>
-  <si>
-    <t>Hassen Taher Dorrah</t>
-  </si>
-  <si>
-    <t>Hesham N. Elmahdy</t>
-  </si>
-  <si>
-    <t>Hewayda Lotfy</t>
-  </si>
-  <si>
-    <t>Husin Abdelaty</t>
-  </si>
-  <si>
-    <t>Hussein Kotb</t>
-  </si>
-  <si>
-    <t>Islam Ahmed Elmaddah</t>
-  </si>
-  <si>
-    <t>M A Moustafa Hassan</t>
-  </si>
-  <si>
-    <t>M Watheq Khrashy</t>
-  </si>
-  <si>
-    <t>Magdy Aboelela</t>
-  </si>
-  <si>
-    <t>Maryam Nabil</t>
-  </si>
-  <si>
-    <t>Mohamed Abouelatta</t>
-  </si>
-  <si>
-    <t>Mohamed Hesham Farouk</t>
-  </si>
-  <si>
-    <t>Mohamed Rehan</t>
-  </si>
-  <si>
-    <t>Mona Farouk</t>
-  </si>
-  <si>
-    <t>Prof. Mohamed Abdelaziz</t>
-  </si>
-  <si>
-    <t>Sahar Ali Fawzi</t>
-  </si>
-  <si>
-    <t>Wedad Hussein</t>
-  </si>
-  <si>
-    <t>Yasser Mohammed Sabry Gad Aboelmad</t>
-  </si>
-  <si>
-    <t>email1@example.com</t>
-  </si>
-  <si>
     <t>email2@example.com</t>
   </si>
   <si>
@@ -245,42 +68,6 @@
     <t>email4@example.com</t>
   </si>
   <si>
-    <t>email5@example.com</t>
-  </si>
-  <si>
-    <t>email6@example.com</t>
-  </si>
-  <si>
-    <t>email7@example.com</t>
-  </si>
-  <si>
-    <t>email8@example.com</t>
-  </si>
-  <si>
-    <t>email9@example.com</t>
-  </si>
-  <si>
-    <t>email10@example.com</t>
-  </si>
-  <si>
-    <t>email11@example.com</t>
-  </si>
-  <si>
-    <t>email12@example.com</t>
-  </si>
-  <si>
-    <t>email13@example.com</t>
-  </si>
-  <si>
-    <t>email14@example.com</t>
-  </si>
-  <si>
-    <t>email15@example.com</t>
-  </si>
-  <si>
-    <t>email16@example.com</t>
-  </si>
-  <si>
     <t>email17@example.com</t>
   </si>
   <si>
@@ -329,57 +116,6 @@
     <t>email32@example.com</t>
   </si>
   <si>
-    <t>email33@example.com</t>
-  </si>
-  <si>
-    <t>email34@example.com</t>
-  </si>
-  <si>
-    <t>email35@example.com</t>
-  </si>
-  <si>
-    <t>email36@example.com</t>
-  </si>
-  <si>
-    <t>email37@example.com</t>
-  </si>
-  <si>
-    <t>email38@example.com</t>
-  </si>
-  <si>
-    <t>email40@example.com</t>
-  </si>
-  <si>
-    <t>email41@example.com</t>
-  </si>
-  <si>
-    <t>email42@example.com</t>
-  </si>
-  <si>
-    <t>email43@example.com</t>
-  </si>
-  <si>
-    <t>email44@example.com</t>
-  </si>
-  <si>
-    <t>email45@example.com</t>
-  </si>
-  <si>
-    <t>email46@example.com</t>
-  </si>
-  <si>
-    <t>email47@example.com</t>
-  </si>
-  <si>
-    <t>email48@example.com</t>
-  </si>
-  <si>
-    <t>email49@example.com</t>
-  </si>
-  <si>
-    <t>email50@example.com</t>
-  </si>
-  <si>
     <t>email51@example.com</t>
   </si>
   <si>
@@ -410,26 +146,116 @@
     <t>email60@example.com</t>
   </si>
   <si>
-    <t>Nawal Ahmed El-Fishawy</t>
-  </si>
-  <si>
     <t>email61@example.com</t>
   </si>
   <si>
-    <t>Samah El Shafei</t>
-  </si>
-  <si>
-    <t>email62@example.com</t>
-  </si>
-  <si>
-    <t>Mohamed Refky Mohamed</t>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>A19</t>
+  </si>
+  <si>
+    <t>A20</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>A22</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>A24</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>A27</t>
+  </si>
+  <si>
+    <t>A28</t>
+  </si>
+  <si>
+    <t>A29</t>
+  </si>
+  <si>
+    <t>A30</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>A32</t>
+  </si>
+  <si>
+    <t>A1@example.com</t>
+  </si>
+  <si>
+    <t>A2@example.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,6 +275,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -846,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="37.734375" bestFit="1" customWidth="1"/>
@@ -867,9 +699,9 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -878,21 +710,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -900,10 +732,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
@@ -914,18 +746,18 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -933,54 +765,54 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>4</v>
@@ -988,10 +820,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -999,32 +831,32 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1032,10 +864,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>4</v>
@@ -1043,43 +875,43 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1087,10 +919,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>4</v>
@@ -1098,87 +930,87 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
+        <v>62</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>112</v>
+        <v>63</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>4</v>
@@ -1186,21 +1018,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1208,343 +1040,31 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>31</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>8</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" t="s">
-        <v>121</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" t="s">
-        <v>122</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C48" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C60">
-      <sortCondition ref="A1:A48"/>
+  <autoFilter ref="A1:C20" xr:uid="{3A2F7CC1-1E29-49A6-BFB0-78FB543407D2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C32">
+      <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B61" r:id="rId1" xr:uid="{1DA225FB-8F48-4120-BB82-DB3C65C02DF5}"/>
-    <hyperlink ref="B62" r:id="rId2" xr:uid="{03646A07-246B-4A81-B6F7-921957311AD5}"/>
+    <hyperlink ref="B33" r:id="rId1" xr:uid="{1DA225FB-8F48-4120-BB82-DB3C65C02DF5}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{7EFA2CBA-E9C9-4DDD-9AFC-F0E8B35FEC90}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{6C108153-780D-4AA9-9D4C-62E89BCB57D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
